--- a/backend/tests/fixtures/vyapar-sample.xlsx
+++ b/backend/tests/fixtures/vyapar-sample.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24AAACR5055K1Z5</t>
+          <t>24AAACR5055K1ZD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,10 +536,6 @@
           <t>devi@example.com</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Customer</t>
@@ -574,16 +570,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24BBBCC5555K2Z9</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>24BBBCC5555K2ZI</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>GJ</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Supplier</t>
@@ -611,11 +605,6 @@
           <t>9988776655</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Karigar</t>
@@ -626,7 +615,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -634,19 +622,11 @@
           <t>Rajesh Patel</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
